--- a/Sheet/AI/PersonalityKeywordMap.xlsx
+++ b/Sheet/AI/PersonalityKeywordMap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Woo_260126\Moumi_moz.A.I.c_Documents\Sheet\AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53837878-CBFF-4138-A6B7-B75EA3D4BFE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D67B940B-2B3D-461F-8876-F3DDFC39A604}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8130" yWindow="1500" windowWidth="21480" windowHeight="13380" activeTab="1" xr2:uid="{E85E095F-D53A-49C1-B1AC-8D07E0BF2BF1}"/>
+    <workbookView xWindow="4515" yWindow="1950" windowWidth="21480" windowHeight="13380" activeTab="1" xr2:uid="{E85E095F-D53A-49C1-B1AC-8D07E0BF2BF1}"/>
   </bookViews>
   <sheets>
     <sheet name="version" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="71">
   <si>
     <t>활발함</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -102,45 +102,12 @@
     <t>설명</t>
   </si>
   <si>
-    <t>ID</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
-    <t>각 키워드의 고유 ID 번호</t>
-  </si>
-  <si>
-    <t>keyword</t>
-  </si>
-  <si>
     <t>string</t>
   </si>
   <si>
-    <t>각 키워드의 이름 텍스트</t>
-  </si>
-  <si>
-    <t>desc</t>
-  </si>
-  <si>
-    <t>각 키워드를 가진 NPC의 성격 설명 텍스트</t>
-  </si>
-  <si>
-    <t>speechPattern</t>
-  </si>
-  <si>
-    <t>각 키워드를 가진 NPC의 대사 출력 시 패턴 설명 텍스트</t>
-  </si>
-  <si>
-    <t>speechExample</t>
-  </si>
-  <si>
-    <t>각 키워드를 가진 NPC의 대사 출력 예시 텍스트</t>
-  </si>
-  <si>
-    <t>AI NPC가 생성될 때 부여받는 성격 데이터 리스트를 정리한 테이블.</t>
-  </si>
-  <si>
     <t>테이블명</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -150,19 +117,6 @@
   </si>
   <si>
     <t>초안 등록</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>stageRequire</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>각 키워드를 NPC에게 부여할 수 있도록 획득하기 위해 클리어해야 하는 스테이지 ID
-* [Stage-ID] 값 참조</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -322,6 +276,67 @@
   </si>
   <si>
     <t>직감형</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>키워드 ID</t>
+  </si>
+  <si>
+    <t>키워드명</t>
+  </si>
+  <si>
+    <t>키워드 그룹</t>
+  </si>
+  <si>
+    <t>대상 에피소드</t>
+  </si>
+  <si>
+    <t>힌트 빈도 보정</t>
+  </si>
+  <si>
+    <t>직설도 보정</t>
+  </si>
+  <si>
+    <t>선제개입 보정</t>
+  </si>
+  <si>
+    <t>위로 성향 보정</t>
+  </si>
+  <si>
+    <t>감정표현 보정</t>
+  </si>
+  <si>
+    <t>기억 스타일</t>
+  </si>
+  <si>
+    <t>말투 메모</t>
+  </si>
+  <si>
+    <t>성격 키워드를 힌트 빈도/직설도/개입성/위로 성향 등 숫자 파라미터로 변환하는 매핑표.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비고</t>
+  </si>
+  <si>
+    <t>Emotion/Relationship/Puzzle</t>
+  </si>
+  <si>
+    <t>EP1/EP2/EP3/EP4/Common</t>
+  </si>
+  <si>
+    <t>장면형/감정형/구조형/흐름형/직감형</t>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>순수함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pure</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -462,7 +477,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -490,26 +505,23 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -853,10 +865,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.3">
@@ -918,70 +930,69 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E303EB0-5D09-4F96-A4ED-77A8140619A6}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.25" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="55.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="44.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="50.625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="18.875" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.625" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.875" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="25" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="75.375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="68" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="F1" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="I1" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="J1" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="K1" s="14" t="s">
-        <v>44</v>
+      <c r="A1" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="135" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="E2" s="3">
         <v>-2</v>
@@ -999,24 +1010,24 @@
         <v>-2</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="135" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="E3" s="3">
         <v>0</v>
@@ -1034,24 +1045,24 @@
         <v>2</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="135" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="E4" s="3">
         <v>-1</v>
@@ -1069,24 +1080,24 @@
         <v>-2</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="135" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="E5" s="3">
         <v>1</v>
@@ -1104,24 +1115,24 @@
         <v>1</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="135" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="E6" s="3">
         <v>-2</v>
@@ -1139,24 +1150,24 @@
         <v>-1</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>45</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="E7" s="6">
         <v>-1</v>
@@ -1174,11 +1185,44 @@
         <v>-1</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>61</v>
-      </c>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6">
+        <v>2</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6">
+        <v>2</v>
+      </c>
+      <c r="I8" s="6">
+        <v>1</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K8" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1192,37 +1236,40 @@
   <sheetPr>
     <tabColor theme="6"/>
   </sheetPr>
-  <dimension ref="B2:E11"/>
+  <dimension ref="B2:F16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.625" customWidth="1"/>
-    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="46.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="B2" s="7" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D2" s="13"/>
       <c r="E2" s="13"/>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="F2" s="13"/>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
         <v>9</v>
       </c>
@@ -1235,95 +1282,185 @@
       <c r="E5" s="8" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="9">
+      <c r="F5" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="12">
         <v>1</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="9"/>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B7" s="12">
+        <v>2</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="9"/>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B8" s="12">
+        <v>3</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B9" s="12">
+        <v>4</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B10" s="12">
+        <v>5</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="E10" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="9"/>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B11" s="12">
+        <v>6</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="9"/>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B12" s="12">
+        <v>7</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" s="9"/>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B13" s="12">
+        <v>8</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="9"/>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B14" s="12">
+        <v>9</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="9"/>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B15" s="12">
+        <v>10</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="9">
-        <v>2</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" ht="40.5" x14ac:dyDescent="0.3">
-      <c r="B8" s="9">
-        <v>3</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="10" t="s">
+      <c r="E15" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B16" s="12">
+        <v>11</v>
+      </c>
+      <c r="C16" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="9">
-        <v>4</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="9">
-        <v>5</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="9">
-        <v>6</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>24</v>
-      </c>
+      <c r="D16" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C3:F3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
